--- a/outputs/sesi_relatorio_qualidade.xlsx
+++ b/outputs/sesi_relatorio_qualidade.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-15 16:43:44</t>
+          <t>2026-09-18 17:05:53</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:43:44</t>
+          <t>2026-09-18 17:05:53</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-15 16:43:44</t>
+          <t>2026-09-18 17:05:53</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-15 16:43:44</t>
+          <t>2026-09-18 17:05:53</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-15 16:43:44</t>
+          <t>2026-09-18 17:05:53</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-15 16:43:44</t>
+          <t>2026-09-18 17:05:53</t>
         </is>
       </c>
     </row>

--- a/outputs/sesi_relatorio_qualidade.xlsx
+++ b/outputs/sesi_relatorio_qualidade.xlsx
@@ -9,6 +9,12 @@
   <sheets>
     <sheet name="Resumo_Geral" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Resumo_PDFs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="01_Execução Orçamentária (S" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="02_Saldo Exercício Anterior" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="03_Previsão Orçamentária (S" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="04_Rateio de Despesas (SESI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="05_Despesas por Licitação (" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="06_Bens Imóveis (SESI - DN" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -557,11 +563,19 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18 17:59:26</t>
+          <t>2026-09-29 15:50:56</t>
         </is>
       </c>
     </row>
@@ -618,11 +632,19 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:59:26</t>
+          <t>2026-09-29 15:50:56</t>
         </is>
       </c>
     </row>
@@ -679,11 +701,19 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18 17:59:26</t>
+          <t>2026-09-29 15:50:56</t>
         </is>
       </c>
     </row>
@@ -740,11 +770,19 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18 17:59:26</t>
+          <t>2026-09-29 15:50:56</t>
         </is>
       </c>
     </row>
@@ -801,11 +839,19 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18 17:59:26</t>
+          <t>2026-09-29 15:50:56</t>
         </is>
       </c>
     </row>
@@ -862,11 +908,19 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18 17:59:26</t>
+          <t>2026-09-29 15:50:56</t>
         </is>
       </c>
     </row>
@@ -901,4 +955,4350 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DataPublicacao</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Legenda</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Contas.IDItemTransp</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Contas.IDItemTranspSuperior</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Contas.Nivel</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Contas.NMItemTransp</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Contas.ValorEstimada</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Contas.ValorRealizada</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Contas.ExecPerc</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Contas.PesoPerc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RECEITAS DE CONTRIBUIÇÕES</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2120050397.31</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1437014490.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>41010101001</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DIRETAS</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>391593194.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>388249653.05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>41010101002</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>INDIRETAS</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1728457203.01</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1048764837.85</v>
+      </c>
+      <c r="L4" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>41010101004</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ANUIDADE DAS AFILIADAS</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>41010102</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CONTRIBUIÇÃO SINDICAL</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>41010103</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CONTRIBUIÇÃO CONFEDERATIVA</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>41010104</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CONTRIBUIÇÕES REGULAMENTARES ORIUNDAS DO SESI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>41010105</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RECEITAS INSTITUCIONAIS</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>410102</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RECEITAS FINANCEIRAS</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>633810736.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>427370996.44</v>
+      </c>
+      <c r="L10" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>41010201</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>410102</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RECEITAS IMOBILIÁRIAS</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>776149.02</v>
+      </c>
+      <c r="K11" t="n">
+        <v>260000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>41010202</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>410102</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RECEITAS DE VALORES MOBILIÁRIOS</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>633034587.23</v>
+      </c>
+      <c r="K12" t="n">
+        <v>427110996.44</v>
+      </c>
+      <c r="L12" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>410103</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RECEITAS INDUSTRIAIS</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>41010301</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>410103</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>RECEITA DA INDÚSTRIA DE PRODUTOS ALIMENTARES</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>41010302</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>410103</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RECEITAS DE ARTIGOS CONFECCIONADOS EM CURSOS</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>410104</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RECEITAS DE SERVIÇOS E VENDAS</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>119954651.08</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4235446.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>41010401</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>410104</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SERVIÇOS E VENDAS COMERCIAIS</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>118308686.44</v>
+      </c>
+      <c r="K17" t="n">
+        <v>155568.49</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>41010402</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>410104</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SERVIÇOS TECNOLÓGICOS</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>41010403</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>410104</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SERVIÇOS DE CONSULTORIA E ASSISTÊNCIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>670399.47</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3042944.51</v>
+      </c>
+      <c r="L19" t="n">
+        <v>453.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>41010404</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>410104</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SERVIÇOS FINANCEIROS</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Superintendência de Gestão Estratégica</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>41010405</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>410104</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SERVIÇOS ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>239228.98</v>
+      </c>
+      <c r="K21" t="n">
+        <v>48405.33</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DataPublicacao</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Legenda</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Contas.IDItemTransp</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Contas.IDItemTranspSuperior</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Contas.Nivel</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Contas.NMItemTransp</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Contas.ValorEstimada</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Contas.ValorRealizada</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Contas.ExecPerc</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Contas.PesoPerc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>GESTÃO</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DESENVOLVIMENTO INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EDUCAÇÃO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SAÚDE E SEGURANÇA NA INDÚSTRIA</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CULTURA</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COOPERAÇÃO SOCIAL</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SUPORTE AO NEGÓCIO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>APOIO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>OUTRAS INICIATIVAS</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SALDOEXERCANT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>O Departamento Nacional do SESI não possui previsão de utilização de Saldo de Exercícios Anteriores, para este ano.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TOTAIS</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TextoAprovacao</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Contas.IDContaContabil</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Contas.IDContaContabilSuperior</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Contas.NMContaContabil</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Contas.DespesaReceita</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Contas.Orcado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>41010101</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Contribuições Sociais</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>8480201587.33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>41010101001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>41010101</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diretas</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1566372777.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>41010101002</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41010101</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Indiretas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>6913828810.13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>41010104</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Contribuições Regulamentares/Regimentais</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>106002519.86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>41010201</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Receitas Imobiliárias</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>39741122.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>41010202</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Receitas de Valores Mobiliários</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1987610754.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>41010301</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Receita da Indústria de Produtos Alimentares</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>380782490.49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>41010401</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Serviços e Vendas Comerciais</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>559914357.91</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>41010402</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Serviços Tecnológicos</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>9462395.58</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>41010403</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Serviços de Consultoria e Assistência Técnica</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>53762252.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>41010405</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Serviços Administrativos</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>4889664.04</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>41010406</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Serviços de Saúde</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1028944441.47</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>41010407</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Serviços de Educacionais</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1910776844.21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>41010408</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Serviços Lazer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>347566246.08</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>41010409</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Serviços Laboratoriais</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4564179.32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>41010501</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Recuperação  de Despesas</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>260899489.82</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>41010502</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Multas e Juros de Mora</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>20271711.92</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>41010503</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Descontos Obtidos</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1952746.54</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>41010504</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>IDENIZACOES, RESTITUICOES E DOACOES</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>90065236.02</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Jan - Dez</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>O Conselho  Nacional do Serviço Social da Indústria (SESI), em 28/07/2026, no uso das suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do SISTEMA SESI, para o exercício de 2026 (Resolução SESI/CN Nº 0044/2026).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PREVORC_REC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>41010505</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Saldo de Exercícios Anteriores</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>278521064.43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Legenda</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>DataPublicacao</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Areas.Area</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Areas.Objetos.Objeto</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Areas.Objetos.Criterio</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Areas.Objetos.PercSESI</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Areas.Objetos.PercSENAI</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Areas.Objetos.PercCNI</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Areas.Objetos.PercIEL</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Areas.Objetos.PercOutras</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Diretoria Corporativa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gestão e Suporte às atividades da Diretoria Corporativa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos departamentos regionais do SESI e SENAI e Sede das Federações e do IEL.</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Diretoria Corporativa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Gestão de Pessoal e Encargos - Diretoria Corporativa</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Estabelecido em documento próprio.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>33</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="n">
+        <v>33</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Diretoria de Comunicação</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Gestão e Suporte as Atividades - Diretoria de Comunicação</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos departamentos regionais do SESI e SENAI e Sede das Federações e do IEL.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Diretoria de Comunicação</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Geração SESI SENAI</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Atendimento igualitário</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Diretoria Jurídica</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Encontro Nacional dos Advogados do Sistema Indústria - ENASI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos departamentos regionais do SESI e SENAI e Sede das Federações e do IEL.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Diretoria Jurídica</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sistema Juridico de Controle de Processos - SUPER JURIS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Estabelecido em documento próprio (Contrato SUPER JURIS)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H7" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Diretoria Jurídica</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Formulação Estratégica</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Percentual de representação das Entidades</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H8" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Diretoria Jurídica</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gestão e Sup. da Dir. Jurídica</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Média do tempo utilizado na elaboração ou prestação de todos os processos jurídicos e seus subprodutos da área e gerências vinculadas.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="H9" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gabinete da Presidência</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gestão de Adm, Relações Publícas, Eventos Institucionais - Presidência</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos departamentos regionais do SESI e SENAI e Sede das Federações e do IEL.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gerência CNI SP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Gestão da Gerência CNI São Paulo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos departamentos regionais do SESI e SENAI e Sede das Federações e do IEL.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sup. de Negócios Jurídicos e Controle Externo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tribunal de Contas da União (TCU)- Controladoria Geral da União (CGU)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tempo utilizado na elaboração ou prestação de todos os processos jurídicos e subprodutos da área.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="G12" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sup. de Negócios Jurídicos e Controle Externo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gestão e suporte da Ger. de Negócios Jurídicos</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Média do tempo utilizado na elaboração ou prestação de todos os processos jurídicos e seus subprodutos da área e gerências vinculadas.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="G13" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="H13" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Superintendência de Compliance e Integridade</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gestão e Adm - Compliance e Integridade</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos departamentos regionais do SESI e SENAI e Sede das Federações e do IEL.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="G14" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Superintendência de Compliance e Integridade</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gestão e Adm - Comitê de Ética</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Atendimento Igualitário</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>25</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Superintendência de Consultivo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Gestão da Superintendência de Consultivo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Média do tempo utilizado na elaboração ou prestação de todos os processos jurídicos e seus subprodutos da área e gerências vinculadas.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="G16" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Superintendência de Consultivo</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gestão e Sup. da Ger. de Consultoria</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Tempo utilizado na elaboração ou prestação de todos os processos jurídicos e subprodutos da área.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H17" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Superintendência de Consultivo</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ger de Assuntos Institucionais</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Tempo utilizado na elaboração ou prestação de todos os processos jurídicos e subprodutos da área.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="H18" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Superintendência de Contencioso</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Gestão da Superintendência de Contencioso</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Média do tempo utilizado na elaboração ou prestação de todos os processos jurídicos e seus subprodutos da área e gerências vinculadas.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="H19" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Superintendência de Contencioso</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Gestão dos Custos Processuais</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Custas processuais por Entidade.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="G20" t="n">
+        <v>74.59</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20/02/2026 14:21</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Superintendência de Contencioso</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gestão e Sup. da Ger. de Contencioso</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Tempo utilizado na elaboração ou prestação de todos os processos jurídicos e subprodutos da área.</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="G21" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DataPublicacao</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Licitacoes.Periodo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Licitacoes.Tipo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Licitacoes.Total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Licitacoes.PercTotalGeral</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Licitacoes.Composicao.Regulamento</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Licitacoes.Composicao.Modalidade_Forma</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Licitacoes.Composicao.DespesaRealizada</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Licitacoes.Composicao.Percentual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitações e Processos de Seleção</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>152145191.57</v>
+      </c>
+      <c r="E2" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>RLC</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Concorrência</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>13151859.59</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitações e Processos de Seleção</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>152145191.57</v>
+      </c>
+      <c r="E3" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RLC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Convite</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>152662.43</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Licitações e Processos de Seleção</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>152145191.57</v>
+      </c>
+      <c r="E4" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RLC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Licitações e Processos de Seleção</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>152145191.57</v>
+      </c>
+      <c r="E5" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RLC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leilão</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Licitações e Processos de Seleção</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>152145191.57</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RLC</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pregão Eletrônico</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>26914483.95</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17.69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Licitações e Processos de Seleção</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>152145191.57</v>
+      </c>
+      <c r="E7" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RLC</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pregão</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>36027449.07</v>
+      </c>
+      <c r="I7" t="n">
+        <v>23.68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Licitações e Processos de Seleção</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>152145191.57</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>RCA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Seleção com disputa - aberta</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>61257326.39</v>
+      </c>
+      <c r="I8" t="n">
+        <v>40.26</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Licitações e Processos de Seleção</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>152145191.57</v>
+      </c>
+      <c r="E9" t="n">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RCA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Seleção com disputa - fechada</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>14641410.14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.619999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Contratação Direta</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>48225033.58</v>
+      </c>
+      <c r="E10" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RLC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Inexigibilidade</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>6881938.94</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14.27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Contratação Direta</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>48225033.58</v>
+      </c>
+      <c r="E11" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>RLC</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dispensa</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>10852560.21</v>
+      </c>
+      <c r="I11" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Contratação Direta</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>48225033.58</v>
+      </c>
+      <c r="E12" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>RCA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Seleção sem disputa</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>30490534.43</v>
+      </c>
+      <c r="I12" t="n">
+        <v>63.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jan - Jul</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>200370225.15</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DataPublicacao</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Legenda</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Contas.IDItemTransp</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Contas.IDItemTranspSuperior</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Contas.Nivel</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Contas.NMItemTransp</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Contas.ValorEstimada</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Contas.ValorRealizada</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Contas.ExecPerc</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Contas.PesoPerc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BENSIMOVEIS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026.  
+Informa-se que o Departamento Nacional do SESI/SENAI não realiza o pagamento de jetons aos membros do Conselho Nacional. Dessa forma, não há registro de despesas dessa natureza na execução orçamentária da unidade</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>32010102001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TERRENOS</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BENSIMOVEIS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026.  
+Informa-se que o Departamento Nacional do SESI/SENAI não realiza o pagamento de jetons aos membros do Conselho Nacional. Dessa forma, não há registro de despesas dessa natureza na execução orçamentária da unidade</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>32010102002</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PRÉDIOS</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BENSIMOVEIS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026.  
+Informa-se que o Departamento Nacional do SESI/SENAI não realiza o pagamento de jetons aos membros do Conselho Nacional. Dessa forma, não há registro de despesas dessa natureza na execução orçamentária da unidade</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>32010102003</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CONSTRUÇÕES EM ANDAMENTO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>10436451.65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3430291.19</v>
+      </c>
+      <c r="L4" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BENSIMOVEIS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026.  
+Informa-se que o Departamento Nacional do SESI/SENAI não realiza o pagamento de jetons aos membros do Conselho Nacional. Dessa forma, não há registro de despesas dessa natureza na execução orçamentária da unidade</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>32010102004</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>INSTALAÇÕES</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2980143</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BENSIMOVEIS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026.  
+Informa-se que o Departamento Nacional do SESI/SENAI não realiza o pagamento de jetons aos membros do Conselho Nacional. Dessa forma, não há registro de despesas dessa natureza na execução orçamentária da unidade</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>32010102005</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BENFEITORIAS EM IMÓVEIS DE TERCEIROS</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BENSIMOVEIS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026.  
+Informa-se que o Departamento Nacional do SESI/SENAI não realiza o pagamento de jetons aos membros do Conselho Nacional. Dessa forma, não há registro de despesas dessa natureza na execução orçamentária da unidade</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>32010102999</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OUTROS BENS IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>14/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jan - Ago</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BENSIMOVEIS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superintendência de Gestão Estratégica </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Valores Aprovados no Plano de Ação e Orçamento Retificado 2026.  
+Informa-se que o Departamento Nacional do SESI/SENAI não realiza o pagamento de jetons aos membros do Conselho Nacional. Dessa forma, não há registro de despesas dessa natureza na execução orçamentária da unidade</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TOTAIS</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>13416594.65</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3430291.19</v>
+      </c>
+      <c r="L8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>